--- a/data/trans_orig/Q5417-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5417-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de moverse de la cama a una silla que esté al lado de la misma en 2007</t>
+          <t>Población según si es capaz de moverse de la cama a una silla que esté al lado de la misma en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4227</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>892</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8591</t>
+          <t>9124</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>903</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>10091</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>5939</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10662</t>
+          <t>10475</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12219</t>
+          <t>13028</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15829</t>
+          <t>16165</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13588</t>
+          <t>14037</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32854</t>
+          <t>33751</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20765</t>
+          <t>20490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42236</t>
+          <t>42578</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>354776</t>
+          <t>354114</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>367072</t>
+          <t>367018</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>546290</t>
+          <t>545837</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>567979</t>
+          <t>567773</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>906871</t>
+          <t>906174</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>931951</t>
+          <t>931596</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -1302,97 +1302,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1875</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5762</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>9,26%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>5663</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>6655</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>6801</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -1415,97 +1415,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1875</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>1922</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>83994</t>
+          <t>83871</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55108</t>
+          <t>54942</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>141928</t>
+          <t>141898</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>149496</t>
+          <t>149471</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -1871,97 +1871,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1984,97 +1984,97 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>4719</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>17,56%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>926</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>4186</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>5399</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>15,57%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>926</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>4080</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -2097,97 +2097,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1274</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5930</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>22,06%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1274</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6412</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>7520</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>23,85%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1274</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>7583</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39010</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41194</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19638</t>
+          <t>20217</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60601</t>
+          <t>58920</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>11284</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10847</t>
+          <t>11530</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5969</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11851</t>
+          <t>11822</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14087</t>
+          <t>14171</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17483</t>
+          <t>15871</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15708</t>
+          <t>15652</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>35242</t>
+          <t>35321</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>23106</t>
+          <t>23435</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>46745</t>
+          <t>46665</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>481003</t>
+          <t>483452</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>495606</t>
+          <t>495829</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>630461</t>
+          <t>629853</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>653490</t>
+          <t>653390</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1118939</t>
+          <t>1118150</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1145238</t>
+          <t>1144688</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de moverse de la cama a una silla que esté al lado de la misma en 2012</t>
+          <t>Población según si es capaz de moverse de la cama a una silla que esté al lado de la misma en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12517</t>
+          <t>12572</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>5624</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19028</t>
+          <t>19978</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9732</t>
+          <t>9774</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26852</t>
+          <t>28259</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13296</t>
+          <t>14099</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6489</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22969</t>
+          <t>22545</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9710</t>
+          <t>9844</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29241</t>
+          <t>28778</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>6553</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20339</t>
+          <t>21765</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24977</t>
+          <t>24778</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48542</t>
+          <t>48228</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34769</t>
+          <t>35781</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>62128</t>
+          <t>63234</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>380063</t>
+          <t>378841</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399384</t>
+          <t>399915</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>558622</t>
+          <t>557972</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>589002</t>
+          <t>588907</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>946996</t>
+          <t>947344</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>983891</t>
+          <t>984411</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,85%</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>5119</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>992</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>8661</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -3922,97 +3922,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2146</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2040</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2115</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>5586</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4999</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7803</t>
+          <t>7452</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>112263</t>
+          <t>111358</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>73534</t>
+          <t>72860</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>81967</t>
+          <t>81986</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>189336</t>
+          <t>190088</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>199629</t>
+          <t>199621</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -4378,97 +4378,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2222</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2331</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4491,97 +4491,97 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5753</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>4,94%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>25,86%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>1100</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>5031</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>5529</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>22,61%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>4900</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,62 +4639,62 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>986</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2222</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5195</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>986</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4903</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20352</t>
+          <t>21883</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17215</t>
+          <t>16493</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42721</t>
+          <t>42215</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>3104</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14818</t>
+          <t>14488</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6898</t>
+          <t>7695</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22688</t>
+          <t>22754</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12782</t>
+          <t>12734</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31358</t>
+          <t>31636</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12709</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7425</t>
+          <t>7621</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24298</t>
+          <t>23541</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9872</t>
+          <t>10683</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30271</t>
+          <t>30010</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8432</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24534</t>
+          <t>24542</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25106</t>
+          <t>26435</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>48905</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>37151</t>
+          <t>38366</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>65239</t>
+          <t>67028</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>521570</t>
+          <t>522689</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>542817</t>
+          <t>542791</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>659108</t>
+          <t>656602</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>689977</t>
+          <t>689659</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1189390</t>
+          <t>1189859</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1226408</t>
+          <t>1227663</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,47%</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de moverse de la cama a una silla que esté al lado de la misma en 2016</t>
+          <t>Población según si es capaz de moverse de la cama a una silla que esté al lado de la misma en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>4417</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3875</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19723</t>
+          <t>19275</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>5036</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20281</t>
+          <t>20228</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12114</t>
+          <t>11680</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8365</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>4116</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15585</t>
+          <t>15436</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15746</t>
+          <t>15486</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18776</t>
+          <t>20186</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41831</t>
+          <t>43554</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26947</t>
+          <t>27969</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>51286</t>
+          <t>52175</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>329166</t>
+          <t>330014</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>344538</t>
+          <t>344339</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>499032</t>
+          <t>496418</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>526771</t>
+          <t>524548</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>834470</t>
+          <t>834494</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>866239</t>
+          <t>864673</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>6406</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,62 +6351,62 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>1804</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2283</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>6418</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1804</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>5978</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>7362</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>905</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>8482</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -6542,97 +6542,97 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1866</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5246</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>1033</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>4321</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>5220</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1033</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>5190</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>191663</t>
+          <t>191656</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>179316</t>
+          <t>179119</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>187139</t>
+          <t>187106</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>368038</t>
+          <t>368468</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>378426</t>
+          <t>378366</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -6885,97 +6885,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1912</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6998,97 +6998,97 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>1912</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9767</t>
+          <t>9185</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34386</t>
+          <t>35833</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27024</t>
+          <t>27228</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>65936</t>
+          <t>66518</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>887</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7169</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>3778</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18581</t>
+          <t>19163</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21961</t>
+          <t>22124</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13034</t>
+          <t>13863</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11576</t>
+          <t>11615</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6441</t>
+          <t>6562</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20366</t>
+          <t>20112</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>4999</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16762</t>
+          <t>18189</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21535</t>
+          <t>20910</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>46184</t>
+          <t>44536</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>30157</t>
+          <t>31046</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>56050</t>
+          <t>58266</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>560102</t>
+          <t>558615</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>576236</t>
+          <t>575571</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>713324</t>
+          <t>714192</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>743544</t>
+          <t>743739</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1281217</t>
+          <t>1280848</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1314046</t>
+          <t>1314276</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de moverse de la cama a una silla que esté al lado de la misma en 2023</t>
+          <t>Población según si es capaz de moverse de la cama a una silla que esté al lado de la misma en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>693</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>4969</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17418</t>
+          <t>16045</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8256</t>
+          <t>8659</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18698</t>
+          <t>19634</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4144</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8387,7 +8387,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10464</t>
+          <t>11022</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11546</t>
+          <t>11370</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>5143</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14207</t>
+          <t>14604</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24094</t>
+          <t>23690</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39306</t>
+          <t>40261</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>31904</t>
+          <t>31875</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>49959</t>
+          <t>50479</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>250989</t>
+          <t>250437</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>261191</t>
+          <t>261155</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>442967</t>
+          <t>441624</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>461917</t>
+          <t>462452</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>698765</t>
+          <t>696899</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>720005</t>
+          <t>719946</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -8823,97 +8823,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1229</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2479</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>442</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2422</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>2492</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>442</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>2844</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>663</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5628</t>
+          <t>5624</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>5319</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>858</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8197</t>
+          <t>8568</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9008</t>
+          <t>8381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15181</t>
+          <t>15260</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>4387</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18468</t>
+          <t>18532</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>261613</t>
+          <t>261964</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>270305</t>
+          <t>270572</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>435941</t>
+          <t>435920</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>452458</t>
+          <t>453120</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>704757</t>
+          <t>703968</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>723434</t>
+          <t>722230</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -9392,97 +9392,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1192</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>816</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9540,62 +9540,62 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>856</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>754</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -9618,97 +9618,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1192</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9731,7 +9731,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>104169</t>
+          <t>104170</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>70431</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>175557</t>
+          <t>175455</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>703</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>4987</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17935</t>
+          <t>17721</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>8310</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19704</t>
+          <t>20130</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>874</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7711</t>
+          <t>7652</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13371</t>
+          <t>13127</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5806</t>
+          <t>5675</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16927</t>
+          <t>16821</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7743</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20350</t>
+          <t>19088</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19500</t>
+          <t>19373</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>51137</t>
+          <t>52611</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>32262</t>
+          <t>34078</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>64558</t>
+          <t>65117</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>620690</t>
+          <t>621835</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>634945</t>
+          <t>634620</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>952620</t>
+          <t>951561</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>999335</t>
+          <t>998345</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1583205</t>
+          <t>1582593</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1625590</t>
+          <t>1625354</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5417-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5417-Estudios-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4231</t>
+          <t>4213</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>893</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9124</t>
+          <t>8627</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>930</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10091</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5939</t>
+          <t>5989</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10475</t>
+          <t>11083</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2299</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13028</t>
+          <t>13620</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16165</t>
+          <t>15528</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14037</t>
+          <t>13964</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33751</t>
+          <t>33660</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20490</t>
+          <t>21102</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42578</t>
+          <t>42174</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>354114</t>
+          <t>354163</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>367018</t>
+          <t>367051</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>545837</t>
+          <t>545172</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>567773</t>
+          <t>568057</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>906174</t>
+          <t>907350</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>931596</t>
+          <t>931969</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5762</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,77 +1548,77 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5266</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>8,46%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1723</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>7187</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>4,78%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>914</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>4578</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>7,36%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1723</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>5650</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>83871</t>
+          <t>83918</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54942</t>
+          <t>55259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>141898</t>
+          <t>141236</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>149471</t>
+          <t>149481</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>4397</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5399</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5930</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7520</t>
+          <t>6795</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20217</t>
+          <t>20280</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>58920</t>
+          <t>60133</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11284</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11530</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>5905</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11822</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2934</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14171</t>
+          <t>13642</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15871</t>
+          <t>16290</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15652</t>
+          <t>16660</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>35321</t>
+          <t>37971</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>23435</t>
+          <t>22421</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>46665</t>
+          <t>45874</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>483452</t>
+          <t>482300</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>495829</t>
+          <t>495536</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>629853</t>
+          <t>630344</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>653390</t>
+          <t>652980</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1118150</t>
+          <t>1118670</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1144688</t>
+          <t>1145320</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12572</t>
+          <t>12842</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5624</t>
+          <t>5430</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19978</t>
+          <t>19131</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9774</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28259</t>
+          <t>26008</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14099</t>
+          <t>12597</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>6582</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22545</t>
+          <t>24305</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>9716</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28778</t>
+          <t>28537</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>7288</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21765</t>
+          <t>20626</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24778</t>
+          <t>24482</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48228</t>
+          <t>48721</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35781</t>
+          <t>35701</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>63234</t>
+          <t>64092</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>378841</t>
+          <t>379912</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399915</t>
+          <t>399293</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>557972</t>
+          <t>558850</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>588907</t>
+          <t>589844</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>947344</t>
+          <t>946363</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>984411</t>
+          <t>982038</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,62%</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5119</t>
+          <t>6044</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>999</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8661</t>
+          <t>9513</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5586</t>
+          <t>5635</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7452</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>111358</t>
+          <t>111281</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>72860</t>
+          <t>73651</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>81986</t>
+          <t>81992</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>190088</t>
+          <t>188869</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>199621</t>
+          <t>199584</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>5437</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21883</t>
+          <t>22119</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16493</t>
+          <t>15417</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42215</t>
+          <t>42194</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14488</t>
+          <t>13701</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7695</t>
+          <t>7188</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22754</t>
+          <t>23286</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12734</t>
+          <t>13225</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31636</t>
+          <t>31804</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13101</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>7835</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23541</t>
+          <t>24353</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10683</t>
+          <t>10724</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30010</t>
+          <t>31159</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>8357</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24542</t>
+          <t>25706</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26435</t>
+          <t>25976</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50929</t>
+          <t>48802</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>38366</t>
+          <t>37665</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>67028</t>
+          <t>65928</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>522689</t>
+          <t>520565</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>542791</t>
+          <t>541850</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>656602</t>
+          <t>659839</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>689659</t>
+          <t>691144</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1189859</t>
+          <t>1189547</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1227663</t>
+          <t>1226823</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4417</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4480</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19275</t>
+          <t>18811</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20228</t>
+          <t>19876</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>2607</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11680</t>
+          <t>12322</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8579</t>
+          <t>8009</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15436</t>
+          <t>15455</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15486</t>
+          <t>15397</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20186</t>
+          <t>19715</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43554</t>
+          <t>43931</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27969</t>
+          <t>27195</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>52175</t>
+          <t>53282</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>330014</t>
+          <t>330730</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>344339</t>
+          <t>344660</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>496418</t>
+          <t>495846</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>524548</t>
+          <t>524792</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>834494</t>
+          <t>833619</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>864673</t>
+          <t>865169</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,21%</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6406</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>7390</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>891</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8482</t>
+          <t>9131</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>185285</t>
+          <t>185162</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>191656</t>
+          <t>191652</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>179119</t>
+          <t>179367</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>187106</t>
+          <t>187108</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>368468</t>
+          <t>367583</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>378366</t>
+          <t>378483</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9185</t>
+          <t>9859</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35833</t>
+          <t>34566</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27228</t>
+          <t>26809</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>66518</t>
+          <t>65844</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7474,42 +7474,42 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>9535</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>4008</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>19338</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
           <t>1,23%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>9535</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>3778</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>19163</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6151</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22124</t>
+          <t>23654</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>3279</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13863</t>
+          <t>13111</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11615</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6562</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20112</t>
+          <t>19775</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4999</t>
+          <t>5617</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18189</t>
+          <t>17839</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20910</t>
+          <t>21881</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>44536</t>
+          <t>47452</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>31046</t>
+          <t>30323</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>58266</t>
+          <t>57573</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>558615</t>
+          <t>559607</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>575571</t>
+          <t>575979</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>714192</t>
+          <t>712047</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>743739</t>
+          <t>742526</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1280848</t>
+          <t>1280645</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1314276</t>
+          <t>1314670</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -8249,32 +8249,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>692</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8284,17 +8284,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10708</t>
+          <t>11538</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>7191</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16045</t>
+          <t>17662</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8319,32 +8319,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12855</t>
+          <t>13651</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8659</t>
+          <t>8699</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19634</t>
+          <t>19641</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -8362,7 +8362,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>917</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -8372,12 +8372,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>4582</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -8387,7 +8387,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8397,32 +8397,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>6474</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3550</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11022</t>
+          <t>11927</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8432,32 +8432,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6563</t>
+          <t>7390</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11370</t>
+          <t>12636</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -8475,32 +8475,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8930</t>
+          <t>9659</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14604</t>
+          <t>16212</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8510,32 +8510,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30947</t>
+          <t>32815</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23690</t>
+          <t>24966</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>40261</t>
+          <t>42189</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8545,22 +8545,22 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>39877</t>
+          <t>42474</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>31875</t>
+          <t>34266</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>50479</t>
+          <t>53802</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -8588,32 +8588,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>256812</t>
+          <t>276905</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>250437</t>
+          <t>269682</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>261155</t>
+          <t>281668</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>453348</t>
+          <t>487954</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>441624</t>
+          <t>476878</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>462452</t>
+          <t>498097</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8658,32 +8658,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>710159</t>
+          <t>764859</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>696899</t>
+          <t>752607</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>719946</t>
+          <t>775298</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,59%</t>
         </is>
       </c>
     </row>
@@ -8701,17 +8701,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>268721</t>
+          <t>289594</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>268721</t>
+          <t>289594</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>268721</t>
+          <t>289594</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>500733</t>
+          <t>538781</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>500733</t>
+          <t>538781</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>500733</t>
+          <t>538781</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>769454</t>
+          <t>828374</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>769454</t>
+          <t>828374</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>769454</t>
+          <t>828374</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>457</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -8863,12 +8863,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>457</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2770</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -8931,32 +8931,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>647</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5624</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8966,32 +8966,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>467</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9001,32 +9001,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8568</t>
+          <t>8775</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -9044,32 +9044,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3664</t>
+          <t>3682</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8381</t>
+          <t>8573</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9079,32 +9079,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7224</t>
+          <t>8592</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15260</t>
+          <t>14194</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9114,32 +9114,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>10888</t>
+          <t>12274</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4387</t>
+          <t>7672</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18532</t>
+          <t>18815</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>267505</t>
+          <t>297884</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>261964</t>
+          <t>292015</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>300950</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>446074</t>
+          <t>266537</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>435920</t>
+          <t>259827</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>453120</t>
+          <t>270393</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>713579</t>
+          <t>564421</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>703968</t>
+          <t>556919</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>722230</t>
+          <t>570102</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>455392</t>
+          <t>277301</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>455392</t>
+          <t>277301</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>455392</t>
+          <t>277301</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>728649</t>
+          <t>581126</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>728649</t>
+          <t>581126</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>728649</t>
+          <t>581126</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9500,7 +9500,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>659</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -9510,12 +9510,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>659</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -9580,12 +9580,12 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>3337</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
@@ -9595,7 +9595,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -9726,27 +9726,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>104828</t>
+          <t>118222</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>104170</t>
+          <t>114899</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -9761,7 +9761,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -9796,27 +9796,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>176153</t>
+          <t>201077</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>175455</t>
+          <t>198399</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9839,17 +9839,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9909,17 +9909,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9956,32 +9956,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>685</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>4657</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9991,32 +9991,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11149</t>
+          <t>11995</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>7704</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17721</t>
+          <t>18624</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10026,32 +10026,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>13296</t>
+          <t>14108</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20130</t>
+          <t>20710</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -10069,32 +10069,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3834</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7652</t>
+          <t>8744</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10104,32 +10104,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7383</t>
+          <t>8188</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13127</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>10461</t>
+          <t>12022</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>7413</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16821</t>
+          <t>18875</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -10182,32 +10182,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12594</t>
+          <t>13341</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7924</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19088</t>
+          <t>19987</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10217,32 +10217,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38171</t>
+          <t>41408</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19373</t>
+          <t>32332</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>52611</t>
+          <t>51783</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10252,32 +10252,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>50765</t>
+          <t>54749</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>34078</t>
+          <t>43958</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>65117</t>
+          <t>67489</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -10295,22 +10295,22 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>629144</t>
+          <t>693012</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>621835</t>
+          <t>684685</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>634620</t>
+          <t>699062</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10330,32 +10330,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>970746</t>
+          <t>837347</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>951561</t>
+          <t>824093</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>998345</t>
+          <t>847044</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10365,32 +10365,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1599890</t>
+          <t>1530357</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1582593</t>
+          <t>1516712</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1625354</t>
+          <t>1543904</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>
@@ -10408,17 +10408,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>646964</t>
+          <t>712300</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>646964</t>
+          <t>712300</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>646964</t>
+          <t>712300</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1027449</t>
+          <t>898937</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1027449</t>
+          <t>898937</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1027449</t>
+          <t>898937</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1674413</t>
+          <t>1611236</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1674413</t>
+          <t>1611236</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1674413</t>
+          <t>1611236</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
